--- a/MAJSushiConfig/ig/StructureDefinition-FRLMResultatExamensBiologieElementCliniquePertinent.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMResultatExamensBiologieElementCliniquePertinent.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMResultatExamensBiologieElementCliniquePertinent</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMResultatExamensBiologieElementCliniquePertinent</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMEntry|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMEntry|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -266,7 +266,7 @@
     <t>FRLMResultatExamensBiologieElementCliniquePertinent.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatient
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient
 </t>
   </si>
   <si>
@@ -301,7 +301,7 @@
     <t>FRLMResultatExamensBiologieElementCliniquePertinent.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
 </t>
   </si>
   <si>
@@ -314,7 +314,7 @@
     <t>FRLMResultatExamensBiologieElementCliniquePertinent.header.author[x].authorOrganisation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation
 </t>
   </si>
   <si>
@@ -327,7 +327,7 @@
     <t>FRLMResultatExamensBiologieElementCliniquePertinent.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDevice
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevice
 </t>
   </si>
   <si>
@@ -340,8 +340,8 @@
     <t>FRLMResultatExamensBiologieElementCliniquePertinent.header.performer[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -389,7 +389,7 @@
     <t>FRLMResultatExamensBiologieElementCliniquePertinent.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMInformant
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMInformant
 </t>
   </si>
   <si>
@@ -479,7 +479,7 @@
     <t>FRLMResultatExamensBiologieElementCliniquePertinent.laboratoireExecutant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMLaboratoireExecutant
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMLaboratoireExecutant
 </t>
   </si>
   <si>
@@ -499,7 +499,7 @@
     <t>FRLMResultatExamensBiologieElementCliniquePertinent.prelevement</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMSpecimen
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSpecimen
 </t>
   </si>
   <si>
@@ -831,7 +831,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.41015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.71484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/MAJSushiConfig/ig/StructureDefinition-FRLMResultatExamensBiologieElementCliniquePertinent.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMResultatExamensBiologieElementCliniquePertinent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
